--- a/LuBan/Design/Datas/技能/Skill.xlsx
+++ b/LuBan/Design/Datas/技能/Skill.xlsx
@@ -37,7 +37,7 @@
     <t>id</t>
   </si>
   <si>
-    <t>timeline_assets</t>
+    <t>skill_timelines_id</t>
   </si>
   <si>
     <t>##type</t>
@@ -1086,7 +1086,7 @@
     <col min="1" max="1" width="8.66666666666667" style="6" customWidth="1"/>
     <col min="2" max="2" width="9" style="6" customWidth="1"/>
     <col min="3" max="3" width="17.4444444444444" style="6" customWidth="1"/>
-    <col min="4" max="4" width="17.4444444444444" style="7" customWidth="1"/>
+    <col min="4" max="4" width="19.2222222222222" style="7" customWidth="1"/>
     <col min="5" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>

--- a/LuBan/Design/Datas/技能/Skill.xlsx
+++ b/LuBan/Design/Datas/技能/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
     <t>##</t>
   </si>
   <si>
-    <t>101001,101002</t>
+    <t>101001</t>
   </si>
   <si>
     <t>SimpleFloatMagnitude</t>
@@ -1081,16 +1081,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="3" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="8.66666666666667" style="6" customWidth="1"/>
+    <col min="1" max="1" width="8.66363636363636" style="6" customWidth="1"/>
     <col min="2" max="2" width="9" style="6" customWidth="1"/>
-    <col min="3" max="3" width="17.4444444444444" style="6" customWidth="1"/>
-    <col min="4" max="4" width="19.2222222222222" style="7" customWidth="1"/>
+    <col min="3" max="3" width="17.4454545454545" style="6" customWidth="1"/>
+    <col min="4" max="4" width="19.2181818181818" style="7" customWidth="1"/>
     <col min="5" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" ht="16.2" spans="1:4">
+    <row r="1" s="4" customFormat="1" spans="1:4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="4" customFormat="1" ht="16.2" spans="1:4">
+    <row r="2" s="4" customFormat="1" spans="1:4">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" s="5" customFormat="1" ht="16.2" spans="1:4">
+    <row r="3" s="5" customFormat="1" spans="1:4">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
@@ -1138,7 +1138,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
@@ -1164,7 +1164,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/LuBan/Design/Datas/技能/Skill.xlsx
+++ b/LuBan/Design/Datas/技能/Skill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>##var</t>
   </si>
@@ -37,22 +37,61 @@
     <t>id</t>
   </si>
   <si>
+    <t>priority</t>
+  </si>
+  <si>
     <t>skill_timelines_id</t>
   </si>
   <si>
+    <t>transform</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
+    <t>Gas.ESkillStagePriority</t>
+  </si>
+  <si>
     <t>(list#sep=,),int</t>
   </si>
   <si>
+    <t>(list#sep=,),int#ref=Gas.TbSkillTransform?</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
+    <t>普通攻击1</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
     <t>101001</t>
+  </si>
+  <si>
+    <t>101004,101003,101002</t>
+  </si>
+  <si>
+    <t>普通攻击2</t>
+  </si>
+  <si>
+    <t>101002</t>
+  </si>
+  <si>
+    <t>普通攻击3</t>
+  </si>
+  <si>
+    <t>101003</t>
+  </si>
+  <si>
+    <t>普通攻击4</t>
+  </si>
+  <si>
+    <t>101004</t>
   </si>
   <si>
     <t>SimpleFloatMagnitude</t>
@@ -1080,51 +1119,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="6" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8.66363636363636" style="6" customWidth="1"/>
     <col min="2" max="2" width="9" style="6" customWidth="1"/>
     <col min="3" max="3" width="17.4454545454545" style="6" customWidth="1"/>
-    <col min="4" max="4" width="19.2181818181818" style="7" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="6"/>
+    <col min="4" max="4" width="26.5454545454545" style="6" customWidth="1"/>
+    <col min="5" max="5" width="19.2181818181818" style="7" customWidth="1"/>
+    <col min="6" max="6" width="48.1818181818182" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" spans="1:4">
+    <row r="1" s="4" customFormat="1" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" s="4" customFormat="1" spans="1:4">
+    <row r="2" s="4" customFormat="1" spans="1:6">
       <c r="A2" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" s="5" customFormat="1" spans="1:4">
+    <row r="3" s="5" customFormat="1" spans="1:6">
       <c r="A3" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" s="5"/>
-      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:6">
       <c r="B4" s="6">
-        <v>1001</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>7</v>
+        <v>101001</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5" s="6">
+        <v>101002</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6" s="6">
+        <v>101003</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7" s="6">
+        <v>101004</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1145,12 +1250,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/LuBan/Design/Datas/技能/Skill.xlsx
+++ b/LuBan/Design/Datas/技能/Skill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -70,28 +70,25 @@
     <t>普通</t>
   </si>
   <si>
-    <t>101001</t>
-  </si>
-  <si>
-    <t>101004,101003,101002</t>
+    <t>1001104,1001103,1001102</t>
   </si>
   <si>
     <t>普通攻击2</t>
   </si>
   <si>
-    <t>101002</t>
-  </si>
-  <si>
     <t>普通攻击3</t>
   </si>
   <si>
-    <t>101003</t>
-  </si>
-  <si>
     <t>普通攻击4</t>
   </si>
   <si>
-    <t>101004</t>
+    <t>冲刺</t>
+  </si>
+  <si>
+    <t>优先</t>
+  </si>
+  <si>
+    <t>1001201</t>
   </si>
   <si>
     <t>SimpleFloatMagnitude</t>
@@ -1119,11 +1116,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8.66363636363636" style="6" customWidth="1"/>
-    <col min="2" max="2" width="9" style="6" customWidth="1"/>
+    <col min="2" max="2" width="10" style="6" customWidth="1"/>
     <col min="3" max="3" width="17.4454545454545" style="6" customWidth="1"/>
     <col min="4" max="4" width="26.5454545454545" style="6" customWidth="1"/>
     <col min="5" max="5" width="19.2181818181818" style="7" customWidth="1"/>
@@ -1175,7 +1172,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="6">
-        <v>101001</v>
+        <v>1001101</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>11</v>
@@ -1183,53 +1180,67 @@
       <c r="D4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6">
+        <v>1001101</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>13</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" s="6">
-        <v>101002</v>
+        <v>1001102</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>16</v>
+      <c r="E5" s="6">
+        <v>1001102</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" s="6">
-        <v>101003</v>
+        <v>1001103</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>18</v>
+      <c r="E6" s="6">
+        <v>1001103</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7" s="6">
-        <v>101004</v>
+        <v>1001104</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>20</v>
+      <c r="E7" s="6">
+        <v>1001104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8" s="6">
+        <v>1001201</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1250,12 +1261,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
